--- a/artfynd/A 23462-2026 artfynd.xlsx
+++ b/artfynd/A 23462-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133786213</v>
       </c>
       <c r="B2" t="n">
-        <v>83344</v>
+        <v>83351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>133786207</v>
       </c>
       <c r="B3" t="n">
-        <v>83208</v>
+        <v>83215</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>133786137</v>
       </c>
       <c r="B4" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>133815753</v>
       </c>
       <c r="B5" t="n">
-        <v>83344</v>
+        <v>83351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23462-2026 artfynd.xlsx
+++ b/artfynd/A 23462-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133786213</v>
+        <v>133784654</v>
       </c>
       <c r="B2" t="n">
-        <v>83351</v>
+        <v>83222</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601940</v>
+        <v>601993</v>
       </c>
       <c r="R2" t="n">
-        <v>7077235</v>
+        <v>7077221</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Elijah Ourth</t>
+          <t>Sofia Gulin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elijah Ourth</t>
+          <t>Sofia Gulin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133786207</v>
+        <v>133784782</v>
       </c>
       <c r="B3" t="n">
-        <v>83215</v>
+        <v>83222</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>601940</v>
       </c>
       <c r="R3" t="n">
-        <v>7077235</v>
+        <v>7077184</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Elijah Ourth</t>
+          <t>Sofia Gulin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elijah Ourth</t>
+          <t>Sofia Gulin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133786137</v>
+        <v>133786207</v>
       </c>
       <c r="B4" t="n">
-        <v>79366</v>
+        <v>83222</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601916</v>
+        <v>601940</v>
       </c>
       <c r="R4" t="n">
-        <v>7077243</v>
+        <v>7077235</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,44 +984,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sofia Gulin</t>
+          <t>Elijah Ourth</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sofia Gulin</t>
+          <t>Elijah Ourth</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133815753</v>
+        <v>133784356</v>
       </c>
       <c r="B5" t="n">
-        <v>83351</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,13 +1031,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601920</v>
+        <v>601993</v>
       </c>
       <c r="R5" t="n">
-        <v>7077223</v>
+        <v>7077221</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1064,9 +1064,19 @@
           <t>2026-05-24</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,15 +1091,433 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Sofia Gulin</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sofia Gulin</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133786137</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hembäcken, Hembäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>601916</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7077243</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sofia Gulin</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sofia Gulin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133785255</v>
+      </c>
+      <c r="B7" t="n">
+        <v>83358</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hembäcken, Hembäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>601807</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7077213</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sofia Gulin</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sofia Gulin</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133786213</v>
+      </c>
+      <c r="B8" t="n">
+        <v>83358</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hembäcken, Hembäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>601940</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7077235</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Elijah Ourth</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Elijah Ourth</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133815753</v>
+      </c>
+      <c r="B9" t="n">
+        <v>83358</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hembäcken, Hembäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>601920</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7077223</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23462-2026 artfynd.xlsx
+++ b/artfynd/A 23462-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784654</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784782</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786207</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784356</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786137</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133785255</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133786213</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1518,8 +1558,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133815753</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>